--- a/erp-server/erp-server-file/src/main/resources/excel/oms/RefundOrder.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/RefundOrder.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>退款单号</t>
   </si>
@@ -74,6 +74,12 @@
     <t>退款数量</t>
   </si>
   <si>
+    <t>创建人</t>
+  </si>
+  <si>
+    <t>审核人</t>
+  </si>
+  <si>
     <t>平台创建时间</t>
   </si>
   <si>
@@ -123,6 +129,12 @@
   </si>
   <si>
     <t>{.refundQty}</t>
+  </si>
+  <si>
+    <t>{.createUserName}</t>
+  </si>
+  <si>
+    <t>{.approveUserName}</t>
   </si>
   <si>
     <t>{.platformCreateTime}</t>
@@ -1099,14 +1111,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="7" width="20.125" customWidth="1"/>
-    <col min="8" max="17" width="20.625" customWidth="1"/>
+    <col min="8" max="19" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1158,58 +1170,70 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:19">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/RefundOrder.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/RefundOrder.xlsx
@@ -1,328 +1,191 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="模板" sheetId="1" r:id="rId1"/>
+    <sheet name="模板" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
-  <si>
-    <t>退款单号</t>
-  </si>
-  <si>
-    <t>平台退款单号</t>
-  </si>
-  <si>
-    <t>平台订单编号</t>
-  </si>
-  <si>
-    <t>销售单号</t>
-  </si>
-  <si>
-    <t>平台</t>
-  </si>
-  <si>
-    <t>店铺</t>
-  </si>
-  <si>
-    <t>状态</t>
-  </si>
-  <si>
-    <t>退款金额</t>
-  </si>
-  <si>
-    <t>退款备注</t>
-  </si>
-  <si>
-    <t>平台SKU</t>
-  </si>
-  <si>
-    <t>SKU</t>
-  </si>
-  <si>
-    <t>产品名称</t>
-  </si>
-  <si>
-    <t>销售数量</t>
-  </si>
-  <si>
-    <t>出库数量</t>
-  </si>
-  <si>
-    <t>退款数量</t>
-  </si>
-  <si>
-    <t>创建人</t>
-  </si>
-  <si>
-    <t>审核人</t>
-  </si>
-  <si>
-    <t>平台创建时间</t>
-  </si>
-  <si>
-    <t>平台退款时间</t>
-  </si>
-  <si>
-    <t>{.code}</t>
-  </si>
-  <si>
-    <t>{.platformRefundNo}</t>
-  </si>
-  <si>
-    <t>{.platformOrderNo}</t>
-  </si>
-  <si>
-    <t>{.soCode}</t>
-  </si>
-  <si>
-    <t>{.platformName}</t>
-  </si>
-  <si>
-    <t>{.shopName}</t>
-  </si>
-  <si>
-    <t>{.statusName}</t>
-  </si>
-  <si>
-    <t>{.completeRefundAmount}</t>
-  </si>
-  <si>
-    <t>{.reason}</t>
-  </si>
-  <si>
-    <t>{.platformSkuNo}</t>
-  </si>
-  <si>
-    <t>{.skuNo}</t>
-  </si>
-  <si>
-    <t>{.productName}</t>
-  </si>
-  <si>
-    <t>{.saleQty}</t>
-  </si>
-  <si>
-    <t>{.outQty}</t>
-  </si>
-  <si>
-    <t>{.refundQty}</t>
-  </si>
-  <si>
-    <t>{.createUserName}</t>
-  </si>
-  <si>
-    <t>{.approveUserName}</t>
-  </si>
-  <si>
-    <t>{.platformCreateTime}</t>
-  </si>
-  <si>
-    <t>{.refundTime}</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="22">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color indexed="8"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color theme="1"/>
       <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -637,161 +500,162 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -845,11 +709,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1109,136 +1036,204 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="7" width="20.125" customWidth="1"/>
-    <col min="8" max="19" width="20.625" customWidth="1"/>
+    <col width="20.125" customWidth="1" style="2" min="1" max="7"/>
+    <col width="20.625" customWidth="1" style="2" min="8" max="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>退款单号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>平台退款单号</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>平台订单编号</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>销售单号</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>平台</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>店铺</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>退款金额</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>退款备注</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>平台SKU</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>产品名称</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>销售数量</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>出库数量</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>退款数量</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>创建人</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>平台创建时间</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>平台退款时间</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:19">
-      <c r="A2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>37</v>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>{.code}</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>{.platformRefundNo}</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>{.platformOrderNo}</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>{.soCode}</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>{.platformName}</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>{.shopName}</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>{.statusName}</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>{.completeRefundAmount}</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>{.reason}</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>{.platformSkuNo}</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>{.skuNo}</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>{.productName}</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>{.saleQty}</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>{.outQty}</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>{.refundQty}</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>{.createUserName}</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>{.platformCreateTime}</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>{.refundTime}</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/erp-server/erp-server-file/src/main/resources/excel/oms/RefundOrder.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/RefundOrder.xlsx
@@ -11,6 +11,119 @@
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+  <si>
+    <t>退款单号</t>
+  </si>
+  <si>
+    <t>平台退款单号</t>
+  </si>
+  <si>
+    <t>平台订单编号</t>
+  </si>
+  <si>
+    <t>销售单号</t>
+  </si>
+  <si>
+    <t>平台</t>
+  </si>
+  <si>
+    <t>店铺</t>
+  </si>
+  <si>
+    <t>状态</t>
+  </si>
+  <si>
+    <t>退款金额</t>
+  </si>
+  <si>
+    <t>退款备注</t>
+  </si>
+  <si>
+    <t>平台SKU</t>
+  </si>
+  <si>
+    <t>SKU</t>
+  </si>
+  <si>
+    <t>产品名称</t>
+  </si>
+  <si>
+    <t>销售数量</t>
+  </si>
+  <si>
+    <t>出库数量</t>
+  </si>
+  <si>
+    <t>退款数量</t>
+  </si>
+  <si>
+    <t>创建人</t>
+  </si>
+  <si>
+    <t>平台创建时间</t>
+  </si>
+  <si>
+    <t>平台退款时间</t>
+  </si>
+  <si>
+    <t>{.code}</t>
+  </si>
+  <si>
+    <t>{.platformRefundNo}</t>
+  </si>
+  <si>
+    <t>{.platformOrderNo}</t>
+  </si>
+  <si>
+    <t>{.soCode}</t>
+  </si>
+  <si>
+    <t>{.platformName}</t>
+  </si>
+  <si>
+    <t>{.shopName}</t>
+  </si>
+  <si>
+    <t>{.statusName}</t>
+  </si>
+  <si>
+    <t>{.completeRefundAmount}</t>
+  </si>
+  <si>
+    <t>{.reason}</t>
+  </si>
+  <si>
+    <t>{.platformSkuNo}</t>
+  </si>
+  <si>
+    <t>{.skuNo}</t>
+  </si>
+  <si>
+    <t>{.productName}</t>
+  </si>
+  <si>
+    <t>{.saleQty}</t>
+  </si>
+  <si>
+    <t>{.outQty}</t>
+  </si>
+  <si>
+    <t>{.refundQty}</t>
+  </si>
+  <si>
+    <t>{.createUserName}</t>
+  </si>
+  <si>
+    <t>{.platformCreateTime}</t>
+  </si>
+  <si>
+    <t>{.refundTime}</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1049,187 +1162,115 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>退款单号</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>平台退款单号</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>平台订单编号</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>销售单号</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>平台</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>店铺</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>退款金额</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>退款备注</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>平台SKU</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>SKU</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>产品名称</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>销售数量</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>出库数量</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>退款数量</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>创建人</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>平台创建时间</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>平台退款时间</t>
-        </is>
+      <c s="1" t="s">
+        <v>0</v>
+      </c>
+      <c s="1" t="s">
+        <v>1</v>
+      </c>
+      <c s="1" t="s">
+        <v>2</v>
+      </c>
+      <c s="1" t="s">
+        <v>3</v>
+      </c>
+      <c s="1" t="s">
+        <v>4</v>
+      </c>
+      <c s="1" t="s">
+        <v>5</v>
+      </c>
+      <c s="1" t="s">
+        <v>6</v>
+      </c>
+      <c s="1" t="s">
+        <v>7</v>
+      </c>
+      <c s="1" t="s">
+        <v>8</v>
+      </c>
+      <c s="1" t="s">
+        <v>9</v>
+      </c>
+      <c s="1" t="s">
+        <v>10</v>
+      </c>
+      <c s="1" t="s">
+        <v>11</v>
+      </c>
+      <c s="1" t="s">
+        <v>12</v>
+      </c>
+      <c s="1" t="s">
+        <v>13</v>
+      </c>
+      <c s="1" t="s">
+        <v>14</v>
+      </c>
+      <c s="1" t="s">
+        <v>15</v>
+      </c>
+      <c s="1" t="s">
+        <v>16</v>
+      </c>
+      <c s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>{.code}</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>{.platformRefundNo}</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>{.platformOrderNo}</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>{.soCode}</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>{.platformName}</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>{.shopName}</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>{.statusName}</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>{.completeRefundAmount}</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>{.reason}</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>{.platformSkuNo}</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>{.skuNo}</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>{.productName}</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t>{.saleQty}</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t>{.outQty}</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t>{.refundQty}</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t>{.createUserName}</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t>{.platformCreateTime}</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t>{.refundTime}</t>
-        </is>
+      <c s="1" t="s">
+        <v>18</v>
+      </c>
+      <c s="1" t="s">
+        <v>19</v>
+      </c>
+      <c s="1" t="s">
+        <v>20</v>
+      </c>
+      <c s="1" t="s">
+        <v>21</v>
+      </c>
+      <c s="1" t="s">
+        <v>22</v>
+      </c>
+      <c s="1" t="s">
+        <v>23</v>
+      </c>
+      <c s="1" t="s">
+        <v>24</v>
+      </c>
+      <c s="1" t="s">
+        <v>25</v>
+      </c>
+      <c s="1" t="s">
+        <v>26</v>
+      </c>
+      <c s="1" t="s">
+        <v>27</v>
+      </c>
+      <c s="1" t="s">
+        <v>28</v>
+      </c>
+      <c s="1" t="s">
+        <v>29</v>
+      </c>
+      <c s="1" t="s">
+        <v>30</v>
+      </c>
+      <c s="1" t="s">
+        <v>31</v>
+      </c>
+      <c s="1" t="s">
+        <v>32</v>
+      </c>
+      <c s="1" t="s">
+        <v>33</v>
+      </c>
+      <c s="1" t="s">
+        <v>34</v>
+      </c>
+      <c s="1" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
